--- a/test/fixtures/xlsx/02_multi_sheet.xlsx
+++ b/test/fixtures/xlsx/02_multi_sheet.xlsx
@@ -1,3 +1,38 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Inventory" sheetId="1" r:id="rId1"/>
+    <sheet name="Customers" sheetId="2" r:id="rId2"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+</sst>
+</file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
